--- a/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
+++ b/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
@@ -4981,11 +4981,11 @@
         </is>
       </c>
       <c r="C13" s="35" t="n">
-        <v>15000</v>
+        <v>26000</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>SET THIS. The money at risk over 14 days. v4 Budget Master carries R250 000 of TikTok across eight months, about R14 600 per fortnight.</t>
+          <t>Agreed 21 Aug: R13 000 a week for agility, so R26 000 across the sprint. v4 Budget Master carries R250 000 across eight months, about R15 625 a fortnight, so this front loads that buy rather than adding to it.</t>
         </is>
       </c>
     </row>

--- a/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
+++ b/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
@@ -4981,26 +4981,26 @@
         </is>
       </c>
       <c r="C13" s="35" t="n">
-        <v>26000</v>
+        <v>10000</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Agreed 21 Aug: R13 000 a week for agility, so R26 000 across the sprint. v4 Budget Master carries R250 000 across eight months, about R15 625 a fortnight, so this front loads that buy rather than adding to it.</t>
+          <t>Agreed 21 Aug: R5 000 a week across both weeks. Sits inside the R250 000 of paid media the v4 plan already carries rather than adding to it.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Qualifying sales target, both engines</t>
+          <t>Qualifying sales target</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>SET THIS. The number the sprint has to bank for the full budget to be released.</t>
+          <t>Agreed 21 Aug. What R10 000 returns if click to sale is 2%, which is the hypothesis being tested. Hitting it confirms 2% and tells exco R2m buys about 12 100 sales, not 40 000.</t>
         </is>
       </c>
     </row>
@@ -5011,11 +5011,11 @@
         </is>
       </c>
       <c r="C15" s="27" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>SET THIS. The rest is carried by school outreach.</t>
+          <t>100% this sprint. The 61 is what the paid budget buys. School outreach carries no media spend and is setting its first baseline, so it is measured rather than targeted.</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Calculated.</t>
+          <t>Calculated. Zero by design this sprint. GE2 sales are counted and reported, just not targeted.</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Calculated. THE TEST. Nobody knows the real rate, because no click has ever been tied to a payment. If this looks high, the target is too high or the cap is too low.</t>
+          <t>Calculated. THE TEST. Nobody knows the real rate, because no click has ever been tied to a payment. For R2m to buy 40 000 this would have to reach 6.6% at today's cost per click.</t>
         </is>
       </c>
     </row>

--- a/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
+++ b/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>The named owner fills yesterday's row in 05_Daily_Log. Blue cells are the only cells anyone types into.</t>
+          <t>The named owner fills yesterday's row in 05_Daily_Log. Yellow cells are the only cells anyone types into.</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Source for all pre-filled targets and budget lines: BridgeApp Phase 2 Operating Workbook v4 (May 2026), sheets 02_Budget_Master, 03_Calendar_Phase2, 04_GE1_Tracker, 05_GE2_Tracker, 10_KPIs_By_GE.</t>
+          <t>Source for all pre-filled targets and budget lines: BridgeApp Phase 2 Operating Workbook v4 (May 2026), sheets 02_Budget_Master, 03_Calendar_Phase2, 04_GE1_Tracker, 05_GE2_Tracker, 09_KPIs_By_GE.</t>
         </is>
       </c>
     </row>

--- a/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
+++ b/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
@@ -1029,7 +1029,7 @@
     <row r="33">
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Sales in this sprint are counted from the Peach transaction export reconciled against the ledger. GA4 cannot attribute a sale until the purchase event is installed. See 03_Sprint_Drivers row 24.</t>
+          <t>Counting sales is a Gradesmatch tech function, not a manual task. It needs either the GA4 purchase event or an automated feed of cleared Peach transactions. Until one of them lands, this workbook has no way to record a sale. See 03_Sprint_Drivers.</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Peach reconciled to ledger by 09:00</t>
+          <t>Peach feed landing daily</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>Campaign Lead</t>
+          <t>Gradesmatch tech</t>
         </is>
       </c>
       <c r="F26" s="72" t="inlineStr">
@@ -3476,12 +3476,12 @@
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Peach reconciliation to ledger</t>
+          <t>Sales counting, Peach to ledger</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Campaign Lead</t>
+          <t>Gradesmatch tech</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Daily by 09:00</t>
+          <t>Automated, daily</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E56"/>
+  <dimension ref="B2:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Peach transaction export, reconciled against the sales ledger daily by 09:00 by the Campaign Lead.</t>
+          <t>An automated feed of cleared Peach transactions, delivered by Gradesmatch tech. This is a tech function. Nobody on the growth team has capacity to reconcile by hand every day.</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="E54" s="33" t="inlineStr">
         <is>
-          <t>Sprint runs on manual Peach reconciliation. Cost per sale is still measurable. Channel attribution is weaker.</t>
+          <t>Without this OR the transaction feed below, no sale can be recorded at all and the sprint measures nothing. With the feed but not this, sales are counted but cannot be split by channel.</t>
         </is>
       </c>
     </row>
@@ -5527,6 +5527,23 @@
       <c r="E56" s="33" t="inlineStr">
         <is>
           <t>Readiness tracker submissions are not captured, so click to signup stays unmeasured and only click to sale can be read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="B57" s="32" t="inlineStr">
+        <is>
+          <t>Automated feed of cleared Peach transactions</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Day 1, 24 Aug</t>
+        </is>
+      </c>
+      <c r="E57" s="33" t="inlineStr">
+        <is>
+          <t>The manual reconciliation this replaces is no longer resourced. Without this or the purchase event there is no way to count a sale.</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5768,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Baseline: closing Peach ledger count recorded in 05_Daily_Log</t>
+          <t>Baseline: closing sales count recorded in 05_Daily_Log</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -5769,9 +5786,9 @@
           <t>PLANNED</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Sprint</t>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>Blocked: dev</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6197,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Mid week reconciliation check against Peach</t>
+          <t>Mid week check that the Peach feed is landing</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -7050,7 +7067,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Final Peach reconciliation for the sprint</t>
+          <t>Final sales count confirmed against the Peach feed</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -7068,9 +7085,9 @@
           <t>PLANNED</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Sprint</t>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>Blocked: dev</t>
         </is>
       </c>
     </row>

--- a/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
+++ b/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
@@ -122,7 +122,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF0B1220"/>
+      <color rgb="FF4A90D9"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -181,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -329,7 +329,10 @@
     <xf numFmtId="2" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1044,40 +1047,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K23"/>
+  <dimension ref="B2:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="74" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2" ht="27" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>UTM REGISTER</t>
+          <t>UTM CODES</t>
         </is>
       </c>
     </row>
     <row r="3" ht="13" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Every link used in the sprint. A link that is not on this sheet cannot be attributed, so the sale it produces counts for nobody.</t>
+          <t>There is one live register and it is not this tab. Links are built and stored in the BridgeApp UTM link builder in Google Drive, so the whole team works off one list.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Type into the yellow cells. Column H builds itself</t>
+          <t>Where links live</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1087,689 +1089,680 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Live register</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>BridgeApp UTM link builder, Google Sheets. Every link is created there and nowhere else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="C7" s="63" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1D7rVlQW8ym0bb20i3-7qmEHBS5fxVVRegwjdhaK9JF8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Why not here</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>A workbook file gets emailed and forked. A Sheet does not. Two registers means links tagged in one and counted from the other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>This tab</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>The checklist of codes this sprint needs. Tick each one off as it is created in the register.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Codes this sprint needs. Tick column H when it exists in the live register.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Campaign</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>Landing URL</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>Tagged URL, copy this one</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>GE</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Created? Y/N</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>Live from</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Meta paid, parent audience</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>paid-social</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>qualifying-sprint</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>meta-set-a</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H7" s="63">
-        <f>IF(OR(G7="",C7="",D7=""),"",G7&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C7))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D7))," ","-"),"/","-"),"--","-")&amp;IF(E7="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E7))," ","-"),"/","-"),"--","-"))&amp;IF(F7="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F7))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I7" s="41" t="inlineStr">
-        <is>
-          <t>GE1</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="K7" s="64" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Meta paid, retargeting July leads</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>paid-social</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>qualifying-sprint</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>meta-retarget</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H8" s="63">
-        <f>IF(OR(G8="",C8="",D8=""),"",G8&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C8))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D8))," ","-"),"/","-"),"--","-")&amp;IF(E8="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E8))," ","-"),"/","-"),"--","-"))&amp;IF(F8="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F8))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I8" s="41" t="inlineStr">
-        <is>
-          <t>GE1</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="K8" s="64" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Google paid search, brand</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>paid-search</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>qualifying-sprint</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H9" s="63">
-        <f>IF(OR(G9="",C9="",D9=""),"",G9&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C9))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D9))," ","-"),"/","-"),"--","-")&amp;IF(E9="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E9))," ","-"),"/","-"),"--","-"))&amp;IF(F9="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F9))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I9" s="41" t="inlineStr">
-        <is>
-          <t>GE1</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="K9" s="64" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>LinkedIn paid, school leaders</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>paid-social</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>qualifying-sprint</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>school-leaders</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H10" s="63">
-        <f>IF(OR(G10="",C10="",D10=""),"",G10&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C10))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D10))," ","-"),"/","-"),"--","-")&amp;IF(E10="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E10))," ","-"),"/","-"),"--","-"))&amp;IF(F10="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F10))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I10" s="41" t="inlineStr">
-        <is>
-          <t>GE1</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="K10" s="64" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Boosted organic, best of last week</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>boosted</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>qualifying-sprint</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>weekly-boost</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H11" s="63">
-        <f>IF(OR(G11="",C11="",D11=""),"",G11&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C11))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D11))," ","-"),"/","-"),"--","-")&amp;IF(E11="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E11))," ","-"),"/","-"),"--","-"))&amp;IF(F11="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F11))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I11" s="41" t="inlineStr">
-        <is>
-          <t>GE1</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="K11" s="64" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Influencer Wave 3, GP creator</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>influencer</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>referral</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>qualifying-sprint</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>wave-3-gp</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H12" s="63">
-        <f>IF(OR(G12="",C12="",D12=""),"",G12&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C12))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D12))," ","-"),"/","-"),"--","-")&amp;IF(E12="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E12))," ","-"),"/","-"),"--","-"))&amp;IF(F12="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F12))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I12" s="41" t="inlineStr">
-        <is>
-          <t>GE1</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="K12" s="64" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Instagram bio link</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>instagram</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>organic-social</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+          <t>Meta paid, parent audience</t>
+        </is>
+      </c>
+      <c r="C13" s="64" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D13" s="64" t="inlineStr">
+        <is>
+          <t>paid-social</t>
+        </is>
+      </c>
+      <c r="E13" s="64" t="inlineStr">
         <is>
           <t>qualifying-sprint</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>bio-link</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H13" s="63">
-        <f>IF(OR(G13="",C13="",D13=""),"",G13&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C13))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D13))," ","-"),"/","-"),"--","-")&amp;IF(E13="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E13))," ","-"),"/","-"),"--","-"))&amp;IF(F13="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F13))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I13" s="41" t="inlineStr">
+      <c r="F13" s="64" t="inlineStr">
+        <is>
+          <t>meta-set-a</t>
+        </is>
+      </c>
+      <c r="G13" s="41" t="inlineStr">
         <is>
           <t>GE1</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="H13" s="40" t="n"/>
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>TBC</t>
         </is>
       </c>
-      <c r="K13" s="64" t="n"/>
+      <c r="J13" s="65" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>WhatsApp concierge broadcast</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>whatsapp</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
+          <t>Meta paid, retargeting July leads</t>
+        </is>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D14" s="64" t="inlineStr">
+        <is>
+          <t>paid-social</t>
+        </is>
+      </c>
+      <c r="E14" s="64" t="inlineStr">
         <is>
           <t>qualifying-sprint</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>broadcast</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H14" s="63">
-        <f>IF(OR(G14="",C14="",D14=""),"",G14&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C14))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D14))," ","-"),"/","-"),"--","-")&amp;IF(E14="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E14))," ","-"),"/","-"),"--","-"))&amp;IF(F14="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F14))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I14" s="41" t="inlineStr">
+      <c r="F14" s="64" t="inlineStr">
+        <is>
+          <t>meta-retarget</t>
+        </is>
+      </c>
+      <c r="G14" s="41" t="inlineStr">
         <is>
           <t>GE1</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="H14" s="40" t="n"/>
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>TBC</t>
         </is>
       </c>
-      <c r="K14" s="64" t="n"/>
+      <c r="J14" s="65" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Nurture emailer</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
+          <t>Meta paid, 20 second recut</t>
+        </is>
+      </c>
+      <c r="C15" s="64" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D15" s="64" t="inlineStr">
+        <is>
+          <t>paid-social</t>
+        </is>
+      </c>
+      <c r="E15" s="64" t="inlineStr">
         <is>
           <t>qualifying-sprint</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>nurture-1</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H15" s="63">
-        <f>IF(OR(G15="",C15="",D15=""),"",G15&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C15))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D15))," ","-"),"/","-"),"--","-")&amp;IF(E15="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E15))," ","-"),"/","-"),"--","-"))&amp;IF(F15="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F15))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I15" s="41" t="inlineStr">
+      <c r="F15" s="64" t="inlineStr">
+        <is>
+          <t>recut-20s</t>
+        </is>
+      </c>
+      <c r="G15" s="41" t="inlineStr">
         <is>
           <t>GE1</t>
         </is>
       </c>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="H15" s="40" t="n"/>
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>TBC</t>
         </is>
       </c>
-      <c r="K15" s="64" t="n"/>
+      <c r="J15" s="65" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>School visit QR, generic</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>school-visits</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>qr</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
+          <t>Meta paid, static statement</t>
+        </is>
+      </c>
+      <c r="C16" s="64" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D16" s="64" t="inlineStr">
+        <is>
+          <t>paid-social</t>
+        </is>
+      </c>
+      <c r="E16" s="64" t="inlineStr">
         <is>
           <t>qualifying-sprint</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr"/>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H16" s="63">
-        <f>IF(OR(G16="",C16="",D16=""),"",G16&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C16))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D16))," ","-"),"/","-"),"--","-")&amp;IF(E16="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E16))," ","-"),"/","-"),"--","-"))&amp;IF(F16="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F16))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I16" s="42" t="inlineStr">
-        <is>
-          <t>GE2</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="F16" s="64" t="inlineStr">
+        <is>
+          <t>static-statement</t>
+        </is>
+      </c>
+      <c r="G16" s="41" t="inlineStr">
+        <is>
+          <t>GE1</t>
+        </is>
+      </c>
+      <c r="H16" s="40" t="n"/>
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>TBC</t>
         </is>
       </c>
-      <c r="K16" s="64" t="n"/>
+      <c r="J16" s="65" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>School visit QR, per school</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>school-visits</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>qr</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
+          <t>Boosted organic, best of last week</t>
+        </is>
+      </c>
+      <c r="C17" s="64" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D17" s="64" t="inlineStr">
+        <is>
+          <t>boosted</t>
+        </is>
+      </c>
+      <c r="E17" s="64" t="inlineStr">
         <is>
           <t>qualifying-sprint</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>school-kingsmead</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H17" s="63">
-        <f>IF(OR(G17="",C17="",D17=""),"",G17&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C17))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D17))," ","-"),"/","-"),"--","-")&amp;IF(E17="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E17))," ","-"),"/","-"),"--","-"))&amp;IF(F17="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F17))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I17" s="42" t="inlineStr">
-        <is>
-          <t>GE2</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="F17" s="64" t="inlineStr">
+        <is>
+          <t>weekly-boost</t>
+        </is>
+      </c>
+      <c r="G17" s="41" t="inlineStr">
+        <is>
+          <t>GE1</t>
+        </is>
+      </c>
+      <c r="H17" s="40" t="n"/>
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>TBC</t>
         </is>
       </c>
-      <c r="K17" s="64" t="n"/>
+      <c r="J17" s="65" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Exhibition and conference QR</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>school-events</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>qr</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
+          <t>Instagram bio link</t>
+        </is>
+      </c>
+      <c r="C18" s="64" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D18" s="64" t="inlineStr">
+        <is>
+          <t>organic-social</t>
+        </is>
+      </c>
+      <c r="E18" s="64" t="inlineStr">
         <is>
           <t>qualifying-sprint</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>sahisa-durban</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H18" s="63">
-        <f>IF(OR(G18="",C18="",D18=""),"",G18&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C18))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D18))," ","-"),"/","-"),"--","-")&amp;IF(E18="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E18))," ","-"),"/","-"),"--","-"))&amp;IF(F18="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F18))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I18" s="42" t="inlineStr">
-        <is>
-          <t>GE2</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="F18" s="64" t="inlineStr">
+        <is>
+          <t>bio-link</t>
+        </is>
+      </c>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>GE1</t>
+        </is>
+      </c>
+      <c r="H18" s="40" t="n"/>
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>TBC</t>
         </is>
       </c>
-      <c r="K18" s="64" t="n"/>
+      <c r="J18" s="65" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Parent info session handout</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
+          <t>Nurture emailer</t>
+        </is>
+      </c>
+      <c r="C19" s="64" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D19" s="64" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E19" s="64" t="inlineStr">
+        <is>
+          <t>qualifying-sprint</t>
+        </is>
+      </c>
+      <c r="F19" s="64" t="inlineStr">
+        <is>
+          <t>nurture-1</t>
+        </is>
+      </c>
+      <c r="G19" s="41" t="inlineStr">
+        <is>
+          <t>GE1</t>
+        </is>
+      </c>
+      <c r="H19" s="40" t="n"/>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="J19" s="65" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>School QR, Pretoria Technical</t>
+        </is>
+      </c>
+      <c r="C20" s="64" t="inlineStr">
         <is>
           <t>school-visits</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D20" s="64" t="inlineStr">
+        <is>
+          <t>qr</t>
+        </is>
+      </c>
+      <c r="E20" s="64" t="inlineStr">
+        <is>
+          <t>qualifying-sprint</t>
+        </is>
+      </c>
+      <c r="F20" s="64" t="inlineStr">
+        <is>
+          <t>school-pretoria-technical</t>
+        </is>
+      </c>
+      <c r="G20" s="42" t="inlineStr">
+        <is>
+          <t>GE2</t>
+        </is>
+      </c>
+      <c r="H20" s="40" t="n"/>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="J20" s="65" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>School QR, Pretoria-Wes</t>
+        </is>
+      </c>
+      <c r="C21" s="64" t="inlineStr">
+        <is>
+          <t>school-visits</t>
+        </is>
+      </c>
+      <c r="D21" s="64" t="inlineStr">
+        <is>
+          <t>qr</t>
+        </is>
+      </c>
+      <c r="E21" s="64" t="inlineStr">
+        <is>
+          <t>qualifying-sprint</t>
+        </is>
+      </c>
+      <c r="F21" s="64" t="inlineStr">
+        <is>
+          <t>school-pretoria-wes</t>
+        </is>
+      </c>
+      <c r="G21" s="42" t="inlineStr">
+        <is>
+          <t>GE2</t>
+        </is>
+      </c>
+      <c r="H21" s="40" t="n"/>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="J21" s="65" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>School QR, Pretoria Girls</t>
+        </is>
+      </c>
+      <c r="C22" s="64" t="inlineStr">
+        <is>
+          <t>school-visits</t>
+        </is>
+      </c>
+      <c r="D22" s="64" t="inlineStr">
+        <is>
+          <t>qr</t>
+        </is>
+      </c>
+      <c r="E22" s="64" t="inlineStr">
+        <is>
+          <t>qualifying-sprint</t>
+        </is>
+      </c>
+      <c r="F22" s="64" t="inlineStr">
+        <is>
+          <t>school-pretoria-girls</t>
+        </is>
+      </c>
+      <c r="G22" s="42" t="inlineStr">
+        <is>
+          <t>GE2</t>
+        </is>
+      </c>
+      <c r="H22" s="40" t="n"/>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="J22" s="65" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>School QR, generic fallback</t>
+        </is>
+      </c>
+      <c r="C23" s="64" t="inlineStr">
+        <is>
+          <t>school-visits</t>
+        </is>
+      </c>
+      <c r="D23" s="64" t="inlineStr">
+        <is>
+          <t>qr</t>
+        </is>
+      </c>
+      <c r="E23" s="64" t="inlineStr">
+        <is>
+          <t>qualifying-sprint</t>
+        </is>
+      </c>
+      <c r="F23" s="64" t="inlineStr"/>
+      <c r="G23" s="42" t="inlineStr">
+        <is>
+          <t>GE2</t>
+        </is>
+      </c>
+      <c r="H23" s="40" t="n"/>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="J23" s="65" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Learner leave behind, printed</t>
+        </is>
+      </c>
+      <c r="C24" s="64" t="inlineStr">
+        <is>
+          <t>school-visits</t>
+        </is>
+      </c>
+      <c r="D24" s="64" t="inlineStr">
         <is>
           <t>print</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E24" s="64" t="inlineStr">
         <is>
           <t>qualifying-sprint</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>info-session</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>https://bridgeapp.co.za/uniapply-parents</t>
-        </is>
-      </c>
-      <c r="H19" s="63">
-        <f>IF(OR(G19="",C19="",D19=""),"",G19&amp;"?utm_source="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(C19))," ","-"),"/","-"),"--","-")&amp;"&amp;utm_medium="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(D19))," ","-"),"/","-"),"--","-")&amp;IF(E19="","","&amp;utm_campaign="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(E19))," ","-"),"/","-"),"--","-"))&amp;IF(F19="","","&amp;utm_content="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(F19))," ","-"),"/","-"),"--","-")))</f>
-        <v/>
-      </c>
-      <c r="I19" s="42" t="inlineStr">
+      <c r="F24" s="64" t="inlineStr">
+        <is>
+          <t>leave-behind</t>
+        </is>
+      </c>
+      <c r="G24" s="42" t="inlineStr">
         <is>
           <t>GE2</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="H24" s="40" t="n"/>
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>TBC</t>
         </is>
       </c>
-      <c r="K19" s="64" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Landing URL is pre-filled with the parent page path. If the page is not deployed by day 1, change column G to the live destination on every row before any spend starts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Source and medium are compulsory. Campaign and content are optional and the formula leaves them out when blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Everything is forced to lower case with spaces turned into hyphens, because GA4 treats Meta and meta as two different sources.</t>
+      <c r="J24" s="65" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Parent take home slip</t>
+        </is>
+      </c>
+      <c r="C25" s="64" t="inlineStr">
+        <is>
+          <t>school-visits</t>
+        </is>
+      </c>
+      <c r="D25" s="64" t="inlineStr">
+        <is>
+          <t>print</t>
+        </is>
+      </c>
+      <c r="E25" s="64" t="inlineStr">
+        <is>
+          <t>qualifying-sprint</t>
+        </is>
+      </c>
+      <c r="F25" s="64" t="inlineStr">
+        <is>
+          <t>parent-slip</t>
+        </is>
+      </c>
+      <c r="G25" s="42" t="inlineStr">
+        <is>
+          <t>GE2</t>
+        </is>
+      </c>
+      <c r="H25" s="40" t="n"/>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="J25" s="65" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Source and medium are compulsory. Campaign and content are optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Everything is lower case with spaces as hyphens, because GA4 treats Meta and meta as two different sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>The landing URL is the parent page. If it is not deployed, repoint every link in the register before any spend starts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>A school visited without its own code produces sales nobody can trace back to the room it started in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>A link that is not in the live register cannot be attributed, so the sale it produces counts for nobody.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C9:J9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1895,11 +1888,11 @@
         <f>'06_GE1_Paid_Media'!$C$11</f>
         <v/>
       </c>
-      <c r="G7" s="65">
+      <c r="G7" s="66">
         <f>'03_Sprint_Drivers'!$C$26</f>
         <v/>
       </c>
-      <c r="H7" s="66">
+      <c r="H7" s="67">
         <f>'03_Sprint_Drivers'!$C$26*2</f>
         <v/>
       </c>
@@ -1938,11 +1931,11 @@
         <f>'06_GE1_Paid_Media'!$C$10</f>
         <v/>
       </c>
-      <c r="G8" s="67">
+      <c r="G8" s="68">
         <f>'03_Sprint_Drivers'!$C$17</f>
         <v/>
       </c>
-      <c r="H8" s="68">
+      <c r="H8" s="69">
         <f>ROUND('03_Sprint_Drivers'!$C$17*0.5,0)</f>
         <v/>
       </c>
@@ -1981,10 +1974,10 @@
         <f>'06_GE1_Paid_Media'!$C$12</f>
         <v/>
       </c>
-      <c r="G9" s="65" t="n">
+      <c r="G9" s="66" t="n">
         <v>85</v>
       </c>
-      <c r="H9" s="66" t="n">
+      <c r="H9" s="67" t="n">
         <v>120</v>
       </c>
       <c r="I9" s="47" t="inlineStr">
@@ -2025,7 +2018,7 @@
       <c r="G10" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="H10" s="69" t="n">
+      <c r="H10" s="70" t="n">
         <v>0.025</v>
       </c>
       <c r="I10" s="47" t="inlineStr">
@@ -2063,10 +2056,10 @@
         <f>'06_GE1_Paid_Media'!$C$15</f>
         <v/>
       </c>
-      <c r="G11" s="65" t="n">
+      <c r="G11" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="66" t="n">
+      <c r="H11" s="67" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="47" t="inlineStr">
@@ -2165,11 +2158,11 @@
         <f>'07_GE2_School_Outreach'!$C$11</f>
         <v/>
       </c>
-      <c r="G15" s="67">
+      <c r="G15" s="68">
         <f>'03_Sprint_Drivers'!$C$18</f>
         <v/>
       </c>
-      <c r="H15" s="68">
+      <c r="H15" s="69">
         <f>ROUND('03_Sprint_Drivers'!$C$18*0.5,0)</f>
         <v/>
       </c>
@@ -2208,11 +2201,11 @@
         <f>'07_GE2_School_Outreach'!$C$24</f>
         <v/>
       </c>
-      <c r="G16" s="65">
+      <c r="G16" s="66">
         <f>'03_Sprint_Drivers'!$C$26</f>
         <v/>
       </c>
-      <c r="H16" s="66">
+      <c r="H16" s="67">
         <f>'03_Sprint_Drivers'!$C$26*2</f>
         <v/>
       </c>
@@ -2251,10 +2244,10 @@
         <f>'07_GE2_School_Outreach'!$C$7</f>
         <v/>
       </c>
-      <c r="G17" s="67" t="n">
+      <c r="G17" s="68" t="n">
         <v>12</v>
       </c>
-      <c r="H17" s="68" t="n">
+      <c r="H17" s="69" t="n">
         <v>8</v>
       </c>
       <c r="I17" s="47" t="inlineStr">
@@ -2292,10 +2285,10 @@
         <f>'07_GE2_School_Outreach'!$C$9</f>
         <v/>
       </c>
-      <c r="G18" s="67" t="n">
+      <c r="G18" s="68" t="n">
         <v>50</v>
       </c>
-      <c r="H18" s="68" t="n">
+      <c r="H18" s="69" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="47" t="inlineStr">
@@ -2333,12 +2326,12 @@
         <f>'07_GE2_School_Outreach'!$C$10</f>
         <v/>
       </c>
-      <c r="G19" s="67" t="inlineStr">
+      <c r="G19" s="68" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H19" s="68" t="inlineStr">
+      <c r="H19" s="69" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
@@ -2378,12 +2371,12 @@
         <f>'07_GE2_School_Outreach'!$C$12</f>
         <v/>
       </c>
-      <c r="G20" s="70" t="inlineStr">
+      <c r="G20" s="71" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H20" s="71" t="inlineStr">
+      <c r="H20" s="72" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
@@ -2484,10 +2477,10 @@
         <f>COUNT('05_Daily_Log'!$D$8:$D$21)</f>
         <v/>
       </c>
-      <c r="G24" s="67" t="n">
+      <c r="G24" s="68" t="n">
         <v>14</v>
       </c>
-      <c r="H24" s="68" t="n">
+      <c r="H24" s="69" t="n">
         <v>12</v>
       </c>
       <c r="I24" s="47" t="inlineStr">
@@ -2503,7 +2496,7 @@
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Links in 09_UTM_Register that build a tagged URL</t>
+          <t>Sprint codes created in the live UTM register</t>
         </is>
       </c>
       <c r="C25" s="37" t="inlineStr">
@@ -2522,13 +2515,13 @@
         </is>
       </c>
       <c r="F25" s="24">
-        <f>COUNTIF('09_UTM_Register'!$H$7:$H$19,"?*")</f>
-        <v/>
-      </c>
-      <c r="G25" s="67" t="n">
+        <f>COUNTIF('09_UTM_Register'!$H$13:$H$25,"Y")</f>
+        <v/>
+      </c>
+      <c r="G25" s="68" t="n">
         <v>13</v>
       </c>
-      <c r="H25" s="68" t="n">
+      <c r="H25" s="69" t="n">
         <v>13</v>
       </c>
       <c r="I25" s="47" t="inlineStr">
@@ -2562,17 +2555,17 @@
           <t>Gradesmatch tech</t>
         </is>
       </c>
-      <c r="F26" s="72" t="inlineStr">
+      <c r="F26" s="73" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G26" s="73" t="inlineStr">
+      <c r="G26" s="74" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H26" s="74" t="inlineStr">
+      <c r="H26" s="75" t="inlineStr">
         <is>
           <t>Any miss</t>
         </is>
@@ -2609,17 +2602,17 @@
           <t>Schools Coordinator</t>
         </is>
       </c>
-      <c r="F27" s="72" t="inlineStr">
+      <c r="F27" s="73" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G27" s="73" t="inlineStr">
+      <c r="G27" s="74" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H27" s="74" t="inlineStr">
+      <c r="H27" s="75" t="inlineStr">
         <is>
           <t>Any miss</t>
         </is>
@@ -2656,17 +2649,17 @@
           <t>Campaign Lead</t>
         </is>
       </c>
-      <c r="F28" s="72" t="inlineStr">
+      <c r="F28" s="73" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G28" s="73" t="inlineStr">
+      <c r="G28" s="74" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H28" s="74" t="inlineStr">
+      <c r="H28" s="75" t="inlineStr">
         <is>
           <t>Any miss</t>
         </is>
@@ -2780,7 +2773,7 @@
         <f>'05_Daily_Log'!$L$22</f>
         <v/>
       </c>
-      <c r="D7" s="67">
+      <c r="D7" s="68">
         <f>'03_Sprint_Drivers'!$C$14</f>
         <v/>
       </c>
@@ -2804,7 +2797,7 @@
         <f>IFERROR(('05_Daily_Log'!$D$22+'07_GE2_School_Outreach'!$C$23)/'05_Daily_Log'!$L$22,0)</f>
         <v/>
       </c>
-      <c r="D8" s="65">
+      <c r="D8" s="66">
         <f>'03_Sprint_Drivers'!$C$26</f>
         <v/>
       </c>
@@ -2828,7 +2821,7 @@
         <f>'06_GE1_Paid_Media'!$C$11</f>
         <v/>
       </c>
-      <c r="D9" s="65">
+      <c r="D9" s="66">
         <f>'03_Sprint_Drivers'!$C$26*2</f>
         <v/>
       </c>
@@ -2852,7 +2845,7 @@
         <f>'07_GE2_School_Outreach'!$C$24</f>
         <v/>
       </c>
-      <c r="D10" s="65">
+      <c r="D10" s="66">
         <f>'03_Sprint_Drivers'!$C$26*2</f>
         <v/>
       </c>
@@ -2876,7 +2869,7 @@
         <f>IF(OR(AND(ISNUMBER('06_GE1_Paid_Media'!$C$11),'06_GE1_Paid_Media'!$C$11&lt;='03_Sprint_Drivers'!$C$26,'06_GE1_Paid_Media'!$C$11&gt;0),AND(ISNUMBER('07_GE2_School_Outreach'!$C$24),'07_GE2_School_Outreach'!$C$24&lt;='03_Sprint_Drivers'!$C$26,'07_GE2_School_Outreach'!$C$24&gt;0)),1,0)</f>
         <v/>
       </c>
-      <c r="D11" s="67" t="n">
+      <c r="D11" s="68" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="43">
@@ -2899,7 +2892,7 @@
         <f>'05_Daily_Log'!$D$22</f>
         <v/>
       </c>
-      <c r="D12" s="65">
+      <c r="D12" s="66">
         <f>'03_Sprint_Drivers'!$C$13</f>
         <v/>
       </c>
@@ -2923,7 +2916,7 @@
         <f>COUNT('05_Daily_Log'!$D$8:$D$21)</f>
         <v/>
       </c>
-      <c r="D13" s="67" t="n">
+      <c r="D13" s="68" t="n">
         <v>14</v>
       </c>
       <c r="E13" s="43">
@@ -2946,7 +2939,7 @@
         <f>COUNTIF(E7:E13,"PASS")</f>
         <v/>
       </c>
-      <c r="D15" s="73" t="n">
+      <c r="D15" s="74" t="n">
         <v>7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">

--- a/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
+++ b/workbooks/bridgeapp_qualifying_sprint_20260824_v1.xlsx
@@ -181,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -347,12 +347,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2136,7 +2130,7 @@
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Sales banked, GE2</t>
+          <t>Registrations banked, GE2</t>
         </is>
       </c>
       <c r="C15" s="37" t="inlineStr">
@@ -2155,7 +2149,7 @@
         </is>
       </c>
       <c r="F15" s="24">
-        <f>'07_GE2_School_Outreach'!$C$11</f>
+        <f>'07_GE2_School_Outreach'!$C$16</f>
         <v/>
       </c>
       <c r="G15" s="68">
@@ -2179,7 +2173,7 @@
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Cost per sale, school engine</t>
+          <t>Cost per registration, school engine</t>
         </is>
       </c>
       <c r="C16" s="37" t="inlineStr">
@@ -2198,7 +2192,7 @@
         </is>
       </c>
       <c r="F16" s="36">
-        <f>'07_GE2_School_Outreach'!$C$24</f>
+        <f>'07_GE2_School_Outreach'!$C$42</f>
         <v/>
       </c>
       <c r="G16" s="66">
@@ -2222,7 +2216,7 @@
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Schools visited</t>
+          <t>Schools contacted</t>
         </is>
       </c>
       <c r="C17" s="37" t="inlineStr">
@@ -2241,14 +2235,18 @@
         </is>
       </c>
       <c r="F17" s="24">
-        <f>'07_GE2_School_Outreach'!$C$7</f>
-        <v/>
-      </c>
-      <c r="G17" s="68" t="n">
-        <v>12</v>
-      </c>
-      <c r="H17" s="69" t="n">
-        <v>8</v>
+        <f>'07_GE2_School_Outreach'!$C$12</f>
+        <v/>
+      </c>
+      <c r="G17" s="68" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="H17" s="69" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
       </c>
       <c r="I17" s="47" t="inlineStr">
         <is>
@@ -2263,7 +2261,7 @@
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Calls plus visits</t>
+          <t>Meetings or presentations secured</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
@@ -2282,14 +2280,18 @@
         </is>
       </c>
       <c r="F18" s="24">
-        <f>'07_GE2_School_Outreach'!$C$9</f>
-        <v/>
-      </c>
-      <c r="G18" s="68" t="n">
-        <v>50</v>
-      </c>
-      <c r="H18" s="69" t="n">
-        <v>30</v>
+        <f>'07_GE2_School_Outreach'!$C$13</f>
+        <v/>
+      </c>
+      <c r="G18" s="68" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="H18" s="69" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
       </c>
       <c r="I18" s="47" t="inlineStr">
         <is>
@@ -2304,7 +2306,7 @@
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Signups captured</t>
+          <t>Learners reached</t>
         </is>
       </c>
       <c r="C19" s="37" t="inlineStr">
@@ -2323,7 +2325,7 @@
         </is>
       </c>
       <c r="F19" s="24">
-        <f>'07_GE2_School_Outreach'!$C$10</f>
+        <f>'07_GE2_School_Outreach'!$C$14</f>
         <v/>
       </c>
       <c r="G19" s="68" t="inlineStr">
@@ -2349,7 +2351,7 @@
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Signups per visit</t>
+          <t>Leads captured</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
@@ -2367,16 +2369,16 @@
           <t>Schools Coordinator</t>
         </is>
       </c>
-      <c r="F20" s="29">
-        <f>'07_GE2_School_Outreach'!$C$12</f>
-        <v/>
-      </c>
-      <c r="G20" s="71" t="inlineStr">
+      <c r="F20" s="24">
+        <f>'07_GE2_School_Outreach'!$C$15</f>
+        <v/>
+      </c>
+      <c r="G20" s="68" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="H20" s="72" t="inlineStr">
+      <c r="H20" s="69" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
@@ -2555,17 +2557,17 @@
           <t>Gradesmatch tech</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="71" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G26" s="74" t="inlineStr">
+      <c r="G26" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H26" s="75" t="inlineStr">
+      <c r="H26" s="73" t="inlineStr">
         <is>
           <t>Any miss</t>
         </is>
@@ -2602,17 +2604,17 @@
           <t>Schools Coordinator</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="71" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G27" s="74" t="inlineStr">
+      <c r="G27" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H27" s="75" t="inlineStr">
+      <c r="H27" s="73" t="inlineStr">
         <is>
           <t>Any miss</t>
         </is>
@@ -2649,17 +2651,17 @@
           <t>Campaign Lead</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="71" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G28" s="74" t="inlineStr">
+      <c r="G28" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H28" s="75" t="inlineStr">
+      <c r="H28" s="73" t="inlineStr">
         <is>
           <t>Any miss</t>
         </is>
@@ -2770,7 +2772,7 @@
         </is>
       </c>
       <c r="C7" s="24">
-        <f>'05_Daily_Log'!$L$22</f>
+        <f>'05_Daily_Log'!$M$22</f>
         <v/>
       </c>
       <c r="D7" s="68">
@@ -2794,7 +2796,7 @@
         </is>
       </c>
       <c r="C8" s="36">
-        <f>IFERROR(('05_Daily_Log'!$D$22+'07_GE2_School_Outreach'!$C$23)/'05_Daily_Log'!$L$22,0)</f>
+        <f>IFERROR(('05_Daily_Log'!$D$22+'07_GE2_School_Outreach'!$C$39)/'05_Daily_Log'!$M$22,0)</f>
         <v/>
       </c>
       <c r="D8" s="66">
@@ -2842,7 +2844,7 @@
         </is>
       </c>
       <c r="C10" s="36">
-        <f>'07_GE2_School_Outreach'!$C$24</f>
+        <f>'07_GE2_School_Outreach'!$C$42</f>
         <v/>
       </c>
       <c r="D10" s="66">
@@ -2855,7 +2857,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Same test, applied to visits.</t>
+          <t>Same test, applied to school outreach.</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2941,7 @@
         <f>COUNTIF(E7:E13,"PASS")</f>
         <v/>
       </c>
-      <c r="D15" s="74" t="n">
+      <c r="D15" s="72" t="n">
         <v>7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3001,7 +3003,7 @@
         </is>
       </c>
       <c r="C20" s="24">
-        <f>('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$L$22)</f>
+        <f>('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$M$22)</f>
         <v/>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -3017,7 +3019,7 @@
         </is>
       </c>
       <c r="C21" s="36">
-        <f>('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$L$22)*IFERROR(('05_Daily_Log'!$D$22+'07_GE2_School_Outreach'!$C$23)/'05_Daily_Log'!$L$22,0)</f>
+        <f>('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$M$22)*IFERROR(('05_Daily_Log'!$D$22+'07_GE2_School_Outreach'!$C$39)/'05_Daily_Log'!$M$22,0)</f>
         <v/>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3033,7 +3035,7 @@
         </is>
       </c>
       <c r="C22" s="36">
-        <f>('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$L$22)*'03_Sprint_Drivers'!$C$26</f>
+        <f>('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$M$22)*'03_Sprint_Drivers'!$C$26</f>
         <v/>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3049,7 +3051,7 @@
         </is>
       </c>
       <c r="C23" s="36">
-        <f>('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$L$22)*IFERROR(('05_Daily_Log'!$D$22+'07_GE2_School_Outreach'!$C$23)/'05_Daily_Log'!$L$22,0)-('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$L$22)*'03_Sprint_Drivers'!$C$26</f>
+        <f>('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$M$22)*IFERROR(('05_Daily_Log'!$D$22+'07_GE2_School_Outreach'!$C$39)/'05_Daily_Log'!$M$22,0)-('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$M$22)*'03_Sprint_Drivers'!$C$26</f>
         <v/>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3081,7 +3083,7 @@
         </is>
       </c>
       <c r="C25" s="24">
-        <f>IFERROR(ROUND(('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$L$22)/('03_Sprint_Drivers'!$C$40-2),0),0)</f>
+        <f>IFERROR(ROUND(('03_Sprint_Drivers'!$C$39-'05_Daily_Log'!$M$22)/('03_Sprint_Drivers'!$C$40-2),0),0)</f>
         <v/>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -7144,7 +7146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:P30"/>
+  <dimension ref="B2:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7154,15 +7156,16 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="2" ht="27" customHeight="1">
@@ -7211,7 +7214,7 @@
           <t>GE2: SCHOOL OUTREACH</t>
         </is>
       </c>
-      <c r="M6" s="46" t="inlineStr">
+      <c r="N6" s="46" t="inlineStr">
         <is>
           <t>CALCULATED</t>
         </is>
@@ -7250,45 +7253,50 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Schools visited</t>
+          <t>Schools contacted</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>Calls</t>
+          <t>Meetings or presentations secured</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>Signups captured</t>
+          <t>Learners reached</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Leads captured</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
+          <t>Registrations</t>
+        </is>
+      </c>
+      <c r="M7" s="11" t="inlineStr">
+        <is>
           <t>Total sales</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>Cumulative</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>Target cum.</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="Q7" s="11" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -7309,23 +7317,24 @@
       <c r="I8" s="26" t="n"/>
       <c r="J8" s="26" t="n"/>
       <c r="K8" s="26" t="n"/>
-      <c r="L8" s="48">
-        <f>G8+K8</f>
-        <v/>
-      </c>
+      <c r="L8" s="26" t="n"/>
       <c r="M8" s="48">
-        <f>SUM($L$8:L8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="49">
+        <f>G8+L8</f>
+        <v/>
+      </c>
+      <c r="N8" s="48">
+        <f>SUM($M$8:M8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C8,0)</f>
         <v/>
       </c>
-      <c r="O8" s="57">
-        <f>M8-N8</f>
-        <v/>
-      </c>
-      <c r="P8" s="12" t="n"/>
+      <c r="P8" s="57">
+        <f>N8-O8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="38" t="n">
@@ -7342,23 +7351,24 @@
       <c r="I9" s="26" t="n"/>
       <c r="J9" s="26" t="n"/>
       <c r="K9" s="26" t="n"/>
-      <c r="L9" s="48">
-        <f>G9+K9</f>
-        <v/>
-      </c>
+      <c r="L9" s="26" t="n"/>
       <c r="M9" s="48">
-        <f>SUM($L$8:L9)</f>
-        <v/>
-      </c>
-      <c r="N9" s="49">
+        <f>G9+L9</f>
+        <v/>
+      </c>
+      <c r="N9" s="48">
+        <f>SUM($M$8:M9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C9,0)</f>
         <v/>
       </c>
-      <c r="O9" s="57">
-        <f>M9-N9</f>
-        <v/>
-      </c>
-      <c r="P9" s="12" t="n"/>
+      <c r="P9" s="57">
+        <f>N9-O9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="38" t="n">
@@ -7375,23 +7385,24 @@
       <c r="I10" s="26" t="n"/>
       <c r="J10" s="26" t="n"/>
       <c r="K10" s="26" t="n"/>
-      <c r="L10" s="48">
-        <f>G10+K10</f>
-        <v/>
-      </c>
+      <c r="L10" s="26" t="n"/>
       <c r="M10" s="48">
-        <f>SUM($L$8:L10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="49">
+        <f>G10+L10</f>
+        <v/>
+      </c>
+      <c r="N10" s="48">
+        <f>SUM($M$8:M10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C10,0)</f>
         <v/>
       </c>
-      <c r="O10" s="57">
-        <f>M10-N10</f>
-        <v/>
-      </c>
-      <c r="P10" s="12" t="n"/>
+      <c r="P10" s="57">
+        <f>N10-O10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="38" t="n">
@@ -7408,23 +7419,24 @@
       <c r="I11" s="26" t="n"/>
       <c r="J11" s="26" t="n"/>
       <c r="K11" s="26" t="n"/>
-      <c r="L11" s="48">
-        <f>G11+K11</f>
-        <v/>
-      </c>
+      <c r="L11" s="26" t="n"/>
       <c r="M11" s="48">
-        <f>SUM($L$8:L11)</f>
-        <v/>
-      </c>
-      <c r="N11" s="49">
+        <f>G11+L11</f>
+        <v/>
+      </c>
+      <c r="N11" s="48">
+        <f>SUM($M$8:M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C11,0)</f>
         <v/>
       </c>
-      <c r="O11" s="57">
-        <f>M11-N11</f>
-        <v/>
-      </c>
-      <c r="P11" s="12" t="n"/>
+      <c r="P11" s="57">
+        <f>N11-O11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="38" t="n">
@@ -7441,23 +7453,24 @@
       <c r="I12" s="26" t="n"/>
       <c r="J12" s="26" t="n"/>
       <c r="K12" s="26" t="n"/>
-      <c r="L12" s="48">
-        <f>G12+K12</f>
-        <v/>
-      </c>
+      <c r="L12" s="26" t="n"/>
       <c r="M12" s="48">
-        <f>SUM($L$8:L12)</f>
-        <v/>
-      </c>
-      <c r="N12" s="49">
+        <f>G12+L12</f>
+        <v/>
+      </c>
+      <c r="N12" s="48">
+        <f>SUM($M$8:M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C12,0)</f>
         <v/>
       </c>
-      <c r="O12" s="57">
-        <f>M12-N12</f>
-        <v/>
-      </c>
-      <c r="P12" s="12" t="n"/>
+      <c r="P12" s="57">
+        <f>N12-O12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="38" t="n">
@@ -7474,23 +7487,24 @@
       <c r="I13" s="26" t="n"/>
       <c r="J13" s="26" t="n"/>
       <c r="K13" s="26" t="n"/>
-      <c r="L13" s="48">
-        <f>G13+K13</f>
-        <v/>
-      </c>
+      <c r="L13" s="26" t="n"/>
       <c r="M13" s="48">
-        <f>SUM($L$8:L13)</f>
-        <v/>
-      </c>
-      <c r="N13" s="49">
+        <f>G13+L13</f>
+        <v/>
+      </c>
+      <c r="N13" s="48">
+        <f>SUM($M$8:M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C13,0)</f>
         <v/>
       </c>
-      <c r="O13" s="57">
-        <f>M13-N13</f>
-        <v/>
-      </c>
-      <c r="P13" s="12" t="n"/>
+      <c r="P13" s="57">
+        <f>N13-O13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="38" t="n">
@@ -7507,23 +7521,24 @@
       <c r="I14" s="26" t="n"/>
       <c r="J14" s="26" t="n"/>
       <c r="K14" s="26" t="n"/>
-      <c r="L14" s="48">
-        <f>G14+K14</f>
-        <v/>
-      </c>
+      <c r="L14" s="26" t="n"/>
       <c r="M14" s="48">
-        <f>SUM($L$8:L14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="49">
+        <f>G14+L14</f>
+        <v/>
+      </c>
+      <c r="N14" s="48">
+        <f>SUM($M$8:M14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C14,0)</f>
         <v/>
       </c>
-      <c r="O14" s="57">
-        <f>M14-N14</f>
-        <v/>
-      </c>
-      <c r="P14" s="12" t="n"/>
+      <c r="P14" s="57">
+        <f>N14-O14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="38" t="n">
@@ -7540,23 +7555,24 @@
       <c r="I15" s="26" t="n"/>
       <c r="J15" s="26" t="n"/>
       <c r="K15" s="26" t="n"/>
-      <c r="L15" s="48">
-        <f>G15+K15</f>
-        <v/>
-      </c>
+      <c r="L15" s="26" t="n"/>
       <c r="M15" s="48">
-        <f>SUM($L$8:L15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="49">
+        <f>G15+L15</f>
+        <v/>
+      </c>
+      <c r="N15" s="48">
+        <f>SUM($M$8:M15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C15,0)</f>
         <v/>
       </c>
-      <c r="O15" s="57">
-        <f>M15-N15</f>
-        <v/>
-      </c>
-      <c r="P15" s="12" t="n"/>
+      <c r="P15" s="57">
+        <f>N15-O15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="38" t="n">
@@ -7573,23 +7589,24 @@
       <c r="I16" s="26" t="n"/>
       <c r="J16" s="26" t="n"/>
       <c r="K16" s="26" t="n"/>
-      <c r="L16" s="48">
-        <f>G16+K16</f>
-        <v/>
-      </c>
+      <c r="L16" s="26" t="n"/>
       <c r="M16" s="48">
-        <f>SUM($L$8:L16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="49">
+        <f>G16+L16</f>
+        <v/>
+      </c>
+      <c r="N16" s="48">
+        <f>SUM($M$8:M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C16,0)</f>
         <v/>
       </c>
-      <c r="O16" s="57">
-        <f>M16-N16</f>
-        <v/>
-      </c>
-      <c r="P16" s="12" t="n"/>
+      <c r="P16" s="57">
+        <f>N16-O16</f>
+        <v/>
+      </c>
+      <c r="Q16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="38" t="n">
@@ -7606,23 +7623,24 @@
       <c r="I17" s="26" t="n"/>
       <c r="J17" s="26" t="n"/>
       <c r="K17" s="26" t="n"/>
-      <c r="L17" s="48">
-        <f>G17+K17</f>
-        <v/>
-      </c>
+      <c r="L17" s="26" t="n"/>
       <c r="M17" s="48">
-        <f>SUM($L$8:L17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="49">
+        <f>G17+L17</f>
+        <v/>
+      </c>
+      <c r="N17" s="48">
+        <f>SUM($M$8:M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C17,0)</f>
         <v/>
       </c>
-      <c r="O17" s="57">
-        <f>M17-N17</f>
-        <v/>
-      </c>
-      <c r="P17" s="12" t="n"/>
+      <c r="P17" s="57">
+        <f>N17-O17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="38" t="n">
@@ -7639,23 +7657,24 @@
       <c r="I18" s="26" t="n"/>
       <c r="J18" s="26" t="n"/>
       <c r="K18" s="26" t="n"/>
-      <c r="L18" s="48">
-        <f>G18+K18</f>
-        <v/>
-      </c>
+      <c r="L18" s="26" t="n"/>
       <c r="M18" s="48">
-        <f>SUM($L$8:L18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="49">
+        <f>G18+L18</f>
+        <v/>
+      </c>
+      <c r="N18" s="48">
+        <f>SUM($M$8:M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C18,0)</f>
         <v/>
       </c>
-      <c r="O18" s="57">
-        <f>M18-N18</f>
-        <v/>
-      </c>
-      <c r="P18" s="12" t="n"/>
+      <c r="P18" s="57">
+        <f>N18-O18</f>
+        <v/>
+      </c>
+      <c r="Q18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="38" t="n">
@@ -7672,23 +7691,24 @@
       <c r="I19" s="26" t="n"/>
       <c r="J19" s="26" t="n"/>
       <c r="K19" s="26" t="n"/>
-      <c r="L19" s="48">
-        <f>G19+K19</f>
-        <v/>
-      </c>
+      <c r="L19" s="26" t="n"/>
       <c r="M19" s="48">
-        <f>SUM($L$8:L19)</f>
-        <v/>
-      </c>
-      <c r="N19" s="49">
+        <f>G19+L19</f>
+        <v/>
+      </c>
+      <c r="N19" s="48">
+        <f>SUM($M$8:M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C19,0)</f>
         <v/>
       </c>
-      <c r="O19" s="57">
-        <f>M19-N19</f>
-        <v/>
-      </c>
-      <c r="P19" s="12" t="n"/>
+      <c r="P19" s="57">
+        <f>N19-O19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="38" t="n">
@@ -7705,23 +7725,24 @@
       <c r="I20" s="26" t="n"/>
       <c r="J20" s="26" t="n"/>
       <c r="K20" s="26" t="n"/>
-      <c r="L20" s="48">
-        <f>G20+K20</f>
-        <v/>
-      </c>
+      <c r="L20" s="26" t="n"/>
       <c r="M20" s="48">
-        <f>SUM($L$8:L20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="49">
+        <f>G20+L20</f>
+        <v/>
+      </c>
+      <c r="N20" s="48">
+        <f>SUM($M$8:M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C20,0)</f>
         <v/>
       </c>
-      <c r="O20" s="57">
-        <f>M20-N20</f>
-        <v/>
-      </c>
-      <c r="P20" s="12" t="n"/>
+      <c r="P20" s="57">
+        <f>N20-O20</f>
+        <v/>
+      </c>
+      <c r="Q20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="38" t="n">
@@ -7738,23 +7759,24 @@
       <c r="I21" s="26" t="n"/>
       <c r="J21" s="26" t="n"/>
       <c r="K21" s="26" t="n"/>
-      <c r="L21" s="48">
-        <f>G21+K21</f>
-        <v/>
-      </c>
+      <c r="L21" s="26" t="n"/>
       <c r="M21" s="48">
-        <f>SUM($L$8:L21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="49">
+        <f>G21+L21</f>
+        <v/>
+      </c>
+      <c r="N21" s="48">
+        <f>SUM($M$8:M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="49">
         <f>ROUND('03_Sprint_Drivers'!$C$14/'03_Sprint_Drivers'!$C$9*C21,0)</f>
         <v/>
       </c>
-      <c r="O21" s="57">
-        <f>M21-N21</f>
-        <v/>
-      </c>
-      <c r="P21" s="12" t="n"/>
+      <c r="P21" s="57">
+        <f>N21-O21</f>
+        <v/>
+      </c>
+      <c r="Q21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="51" t="inlineStr">
@@ -7799,16 +7821,20 @@
         <f>SUM(L8:L21)</f>
         <v/>
       </c>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="53">
+      <c r="M22" s="53">
+        <f>SUM(M8:M21)</f>
+        <v/>
+      </c>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="53">
         <f>'03_Sprint_Drivers'!$C$14</f>
         <v/>
       </c>
-      <c r="O22" s="58">
-        <f>L22-N22</f>
-        <v/>
-      </c>
-      <c r="P22" s="4" t="n"/>
+      <c r="P22" s="58">
+        <f>M22-O22</f>
+        <v/>
+      </c>
+      <c r="Q22" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="22" t="inlineStr">
@@ -7850,47 +7876,52 @@
       </c>
       <c r="H25" s="56" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I25" s="56" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I25" s="56" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="J25" s="56" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K25" s="56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" s="56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M25" s="56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N25" s="56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O25" s="56" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P25" s="56" t="inlineStr">
         <is>
-          <t>Meta set A pulled at 14:00, CTR 0.6%</t>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="Q25" s="56" t="inlineStr">
+        <is>
+          <t>Two schools said yes to a presentation. No learners reached yet.</t>
         </is>
       </c>
     </row>
@@ -7904,28 +7935,35 @@
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Sales are taken from the reconciled Peach export, split by the UTM the buyer arrived through. A sale with no UTM goes in neither engine column and is noted.</t>
+          <t>Sales come from the Gradesmatch tech feed of cleared Peach transactions, split by the UTM the buyer arrived through. A sale with no UTM goes in neither engine column and is noted.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Signups captured (GE2) are parent sign ups taken at a visit, from the QR code or the paper sheet, entered the same day.</t>
+          <t>GE2 has five columns because a school visit produces four things before it produces a sale. Log all of them: the work is real even on a day the sales column stays at zero.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>Registrations is the only GE2 column that counts as a sale. It stays at zero until a presentation has actually been delivered to learners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>Target cum. divides the qualifying target evenly across 14 days. It is a pace line, not a forecast.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="N6:Q6"/>
     <mergeCell ref="E6:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8303,14 +8341,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E24"/>
+  <dimension ref="B2:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="2" ht="27" customHeight="1">
@@ -8323,314 +8361,503 @@
     <row r="3" ht="13" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Owner: Schools Coordinator. Reads from 05_Daily_Log and 08_School_Visits. This engine is measured on the same basis as paid media.</t>
+          <t>Owner: Schools Coordinator. A school visit produces four things before it produces a sale, so all four are tracked here. Reads from 05_Daily_Log.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Sprint to date</t>
+          <t>Read this before wondering why sales say zero</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
     </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Different windows</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>The Pretoria school outreach sprint ran 17 to 28 August. This workbook covers 24 August to 6 September. Week 1 of the outreach sits in the outreach report, not in this log, so entering it here will not move these numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Sales lag the work</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Registrations is the only column that counts as a sale, and it stays at zero until a presentation has actually been delivered to learners. Two weeks of visits producing zero sales is the expected shape, not a failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>What moves instead</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Schools contacted, meetings secured, learners reached and leads captured all move the moment they are logged. That is where the week's work shows up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>The pipeline, 24 August to 6 September</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Schools visited</t>
-        </is>
-      </c>
-      <c r="C7" s="24">
-        <f>SUM('05_Daily_Log'!H8:H21)</f>
-        <v/>
-      </c>
-      <c r="D7" s="60" t="n">
-        <v>12</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6 per week is the visit target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Calls made</t>
-        </is>
-      </c>
-      <c r="C8" s="24">
-        <f>SUM('05_Daily_Log'!I8:I21)</f>
-        <v/>
-      </c>
-      <c r="D8" s="60" t="n">
-        <v>38</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19 per week. Calls plus visits equals the v4 GE2 target of 25 per week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Calls plus visits</t>
-        </is>
-      </c>
-      <c r="C9" s="24">
-        <f>SUM('05_Daily_Log'!H8:H21)+SUM('05_Daily_Log'!I8:I21)</f>
-        <v/>
-      </c>
-      <c r="D9" s="60" t="n">
-        <v>50</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>v4 GE2 KPI. Trigger is below 15 in a week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Signups captured</t>
-        </is>
-      </c>
-      <c r="C10" s="24">
-        <f>SUM('05_Daily_Log'!J8:J21)</f>
-        <v/>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Parent sign ups taken at a visit, same day entry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="C11" s="24">
-        <f>SUM('05_Daily_Log'!K8:K21)</f>
-        <v/>
-      </c>
-      <c r="D11" s="60">
-        <f>'03_Sprint_Drivers'!$C$18</f>
-        <v/>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Peach reconciled, attributed to a school tagged link.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Signups per visit</t>
-        </is>
-      </c>
-      <c r="C12" s="29">
-        <f>IFERROR(SUM('05_Daily_Log'!J8:J21)/SUM('05_Daily_Log'!H8:H21),0)</f>
+          <t>Schools contacted</t>
+        </is>
+      </c>
+      <c r="C12" s="24">
+        <f>SUM('05_Daily_Log'!H8:H21)</f>
         <v/>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>The number that tells you whether visits are worth the travel.</t>
+          <t>Visits, calls and emails that reached someone.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Sales per visit</t>
-        </is>
-      </c>
-      <c r="C13" s="62">
-        <f>IFERROR(SUM('05_Daily_Log'!K8:K21)/SUM('05_Daily_Log'!H8:H21),0)</f>
+          <t>Meetings or presentations secured</t>
+        </is>
+      </c>
+      <c r="C13" s="24">
+        <f>SUM('05_Daily_Log'!I8:I21)</f>
         <v/>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>The school engine equivalent of cost per sale.</t>
+          <t>A booked date, not a maybe.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Signup to sale rate</t>
-        </is>
-      </c>
-      <c r="C14" s="28">
-        <f>IFERROR(SUM('05_Daily_Log'!K8:K21)/SUM('05_Daily_Log'!J8:J21),0)</f>
+          <t>Learners reached</t>
+        </is>
+      </c>
+      <c r="C14" s="24">
+        <f>SUM('05_Daily_Log'!J8:J21)</f>
         <v/>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Compare against the paid engine on 05.</t>
+          <t>Only counts once a presentation has actually been delivered.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Share of GE2 target banked</t>
-        </is>
-      </c>
-      <c r="C15" s="28">
-        <f>IFERROR(SUM('05_Daily_Log'!K8:K21)/'03_Sprint_Drivers'!$C$18,0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="61" t="n">
-        <v>1</v>
+          <t>Leads captured</t>
+        </is>
+      </c>
+      <c r="C15" s="24">
+        <f>SUM('05_Daily_Log'!K8:K21)</f>
+        <v/>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Against the GE2 split of the qualifying target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Sprint cost of this engine. Type into the yellow cells</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Cost line</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Sprint cost (R)</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr"/>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>School activations Wave 2</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>v4 Budget Master, R19 000 for all of Aug 2026. Enter only the portion inside these 14 days.</t>
+          <t>Scanned the QR or signed the sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Registrations</t>
+        </is>
+      </c>
+      <c r="C16" s="24">
+        <f>SUM('05_Daily_Log'!L8:L21)</f>
+        <v/>
+      </c>
+      <c r="D16" s="60">
+        <f>'03_Sprint_Drivers'!$C$18</f>
+        <v/>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The only stage that is a sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Conversion, once there is something to convert</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Information sessions support</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="inlineStr"/>
+          <t>Meetings per school contacted</t>
+        </is>
+      </c>
+      <c r="C20" s="28">
+        <f>IFERROR(SUM('05_Daily_Log'!I8:I21)/SUM('05_Daily_Log'!H8:H21),0)</f>
+        <v/>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>v4 Budget Master, R5 000 across Aug and Sep 2026. Enter the sprint portion.</t>
+          <t>How often a contact turns into a booked date.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Travel and fuel</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="inlineStr"/>
+          <t>Learners per presentation</t>
+        </is>
+      </c>
+      <c r="C21" s="29">
+        <f>IFERROR(SUM('05_Daily_Log'!J8:J21)/SUM('05_Daily_Log'!I8:I21),0)</f>
+        <v/>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Actual, from expense claims.</t>
+          <t>Room size. Tells you what a presentation is worth.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Printed material and QR codes</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr"/>
+          <t>Leads per learner reached</t>
+        </is>
+      </c>
+      <c r="C22" s="28">
+        <f>IFERROR(SUM('05_Daily_Log'!K8:K21)/SUM('05_Daily_Log'!J8:J21),0)</f>
+        <v/>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Actual.</t>
+          <t>How well the QR and the pitch work in the room.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Total GE2 sprint cost</t>
-        </is>
-      </c>
-      <c r="C23" s="36">
-        <f>SUM(C19:C22)</f>
-        <v/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Lead to registration rate</t>
+        </is>
+      </c>
+      <c r="C23" s="28">
+        <f>IFERROR(SUM('05_Daily_Log'!L8:L21)/SUM('05_Daily_Log'!K8:K21),0)</f>
+        <v/>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>The number that decides whether schools can carry a sales target.</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Cost per sale, school engine</t>
-        </is>
-      </c>
-      <c r="C24" s="36">
-        <f>IFERROR(C23/SUM('05_Daily_Log'!K8:K21),0)</f>
-        <v/>
-      </c>
-      <c r="D24" s="59">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Registrations per school contacted</t>
+        </is>
+      </c>
+      <c r="C24" s="62">
+        <f>IFERROR(SUM('05_Daily_Log'!L8:L21)/SUM('05_Daily_Log'!H8:H21),0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>The school engine equivalent of cost per sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Baseline from the outreach report, 17 to 28 August</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Schools visited or contacted</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="n">
+        <v>27</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>GradesMatch and UniApply School Outreach Report, Pretoria, internal, 29 August 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Schools requiring follow-up</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Schools with active opportunities</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Access denied without an appointment</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed Grade 11 presentation dates</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Learners reached</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>UniApply registrations</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>What this engine costs</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Cost line</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Sprint cost (R)</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr"/>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Uber voucher, allocated</t>
+        </is>
+      </c>
+      <c r="C38" s="36" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Allocated for school-to-school travel. Outreach report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Uber voucher, spent to date</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Update after each travel day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Acudeo Family Fun Day stall</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>R1 000 if approved. Not covered by the voucher. Decision needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Printed leave behinds and parent slips</t>
+        </is>
+      </c>
+      <c r="C41" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Printed in house.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Cost per registration, school engine</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>IFERROR(C39/SUM('05_Daily_Log'!L8:L21),0)</f>
+        <v/>
+      </c>
+      <c r="D42" s="59">
         <f>'03_Sprint_Drivers'!$C$26</f>
         <v/>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Directly comparable with the paid media cost per sale on 05. This comparison is the point of the sprint.</t>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Voucher spent divided by registrations. Directly comparable with the paid media cost per sale on 06.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C8:E8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
